--- a/GearSage-client/pkgGear/data_raw/daiwa_line_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_line_import.xlsx
@@ -439,8 +439,8 @@
       <c r="A2" t="str">
         <v>DLN1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v>フィネス ブレイブ Z FINESSE BRAVE Z</v>
@@ -474,8 +474,8 @@
       <c r="A3" t="str">
         <v>DLN1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>BASS-Xフロロ 240 BASS-X FLUORO 240</v>
@@ -509,8 +509,8 @@
       <c r="A4" t="str">
         <v>DLN1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>UVF タトゥーラ センサー×8＋Si2 UVF TATULA SENSOR×8+Si2</v>
@@ -544,8 +544,8 @@
       <c r="A5" t="str">
         <v>DLN1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>スティーズ フロロ X’LINK STEEZ FLUORO X’LINK</v>
@@ -579,8 +579,8 @@
       <c r="A6" t="str">
         <v>DLN1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>モンスター ブレイブ Z MONSTER BRAVE Z</v>
@@ -614,8 +614,8 @@
       <c r="A7" t="str">
         <v>DLN1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>スティーズ デュラブラ マックス STEEZ DURABRA MAX</v>
@@ -649,8 +649,8 @@
       <c r="A8" t="str">
         <v>DLN1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>バス-X フロロ BASS-X FLUORO</v>
@@ -684,8 +684,8 @@
       <c r="A9" t="str">
         <v>DLN1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="str">
         <v>UVF フロッグデュラセンサー×8＋Si2 UVF FROG DURA SENSOR×8+Si2</v>
@@ -719,8 +719,8 @@
       <c r="A10" t="str">
         <v>DLN1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
         <v>バス-X ナイロン BASS-X NYLON</v>
@@ -754,8 +754,8 @@
       <c r="A11" t="str">
         <v>DLN1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="str">
         <v>スティーズフロロ タフネス STEEZ FLUORO TOUGHNESS</v>
@@ -789,8 +789,8 @@
       <c r="A12" t="str">
         <v>DLN1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>タトゥーラ タイプ ナイロン TATULA Type NYLON</v>
@@ -824,8 +824,8 @@
       <c r="A13" t="str">
         <v>DLN1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>プレッソエリアエステル TT PRESSO AREA ESTER TECHNICAL TUNE</v>
@@ -859,8 +859,8 @@
       <c r="A14" t="str">
         <v>DLN1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
         <v>トラウトフロロリーダー TROUT FLUORO LEADER</v>
@@ -894,8 +894,8 @@
       <c r="A15" t="str">
         <v>DLN1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="str">
         <v>プレッソエリアデュラブラMAX PRESSO AREA DURABRAMAX</v>
@@ -929,8 +929,8 @@
       <c r="A16" t="str">
         <v>DLN1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>プレッソ　エリア　TYPE-F PRESSO AREA TYPE F</v>
@@ -964,8 +964,8 @@
       <c r="A17" t="str">
         <v>DLN1015</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>プレッソ タイプN PRESSO TYPE N</v>
@@ -999,8 +999,8 @@
       <c r="A18" t="str">
         <v>DLN1016</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>UVFプレッソエリアデュラセンサー×8EX+Si3 UVF PRESSO AREA DURA SENSOR X8EX+SI3</v>
@@ -1034,8 +1034,8 @@
       <c r="A19" t="str">
         <v>DLN1017</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>月下美人フロロリーダー GEKKABIJIN FLUORO LEADER</v>
@@ -1069,8 +1069,8 @@
       <c r="A20" t="str">
         <v>DLN1018</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>プレッソ エリア TYPE-E PRESSO AREA TYPE-E</v>
@@ -1104,8 +1104,8 @@
       <c r="A21" t="str">
         <v>DLN1019</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>UVF エメラルダスデュラセンサーX8EX+Si3 IM UVF EMERALDAS DURASENSOR X8EX+SI3 IM</v>
@@ -1139,8 +1139,8 @@
       <c r="A22" t="str">
         <v>DLN1020</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>紅牙フロロリーダーEX KOHGA FLUORO LEADER EX</v>
@@ -1174,8 +1174,8 @@
       <c r="A23" t="str">
         <v>DLN1021</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>フロロショックリーダーX FLUORO SHOCK LEADER X</v>
@@ -1209,8 +1209,8 @@
       <c r="A24" t="str">
         <v>DLN1022</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>モアザンリーダーEX II TYPE-F（フロロ） morethan LEADER EX II TYPE-F（FLUORO）</v>
@@ -1244,8 +1244,8 @@
       <c r="A25" t="str">
         <v>DLN1023</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="B25">
+        <v>2</v>
       </c>
       <c r="C25" t="str">
         <v>シルバークリーク TYPE-N（ナイロン） SILVER CREEK TYPE-N</v>
@@ -1279,8 +1279,8 @@
       <c r="A26" t="str">
         <v>DLN1024</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="B26">
+        <v>2</v>
       </c>
       <c r="C26" t="str">
         <v>UVF ソルティガデュラセンサー8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2</v>
@@ -1314,8 +1314,8 @@
       <c r="A27" t="str">
         <v>DLN1025</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>ソルティガ フロロリーダー X’LINK（クロスリンク） SALTIGA FLUORO LEADER X’LINK</v>
@@ -1349,8 +1349,8 @@
       <c r="A28" t="str">
         <v>DLN1026</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>UVF ソルティガ SJ デュラセンサー×8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2</v>
@@ -1384,8 +1384,8 @@
       <c r="A29" t="str">
         <v>DLN1027</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>2</v>
       </c>
       <c r="C29" t="str">
         <v>モアザンデュラブラ MAX MORETHAN DURABRA MAX</v>
@@ -1419,8 +1419,8 @@
       <c r="A30" t="str">
         <v>DLN1028</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>UVF モアザン デュラセンサー×8＋Si² UVF MORETHAN DURASENSOR X8BRAID +Si²</v>
@@ -1454,8 +1454,8 @@
       <c r="A31" t="str">
         <v>DLN1029</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>UVF ソルティガデュラセンサー×12EX+Si3 UVF SALTIGA DURA SENSOR×12EX+Si3</v>
@@ -1489,8 +1489,8 @@
       <c r="A32" t="str">
         <v>DLN1030</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
+      <c r="B32">
+        <v>2</v>
       </c>
       <c r="C32" t="str">
         <v>UVF月下美人デュラセンサー＋Si² UVF GEKKABIJIN DURA SENSOR＋Si²</v>
@@ -1524,8 +1524,8 @@
       <c r="A33" t="str">
         <v>DLN1031</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>2</v>
       </c>
       <c r="C33" t="str">
         <v>ソルティガ ナイロンリーダー SALTIGA NYLON LEADER</v>
@@ -1559,8 +1559,8 @@
       <c r="A34" t="str">
         <v>DLN1032</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>2</v>
       </c>
       <c r="C34" t="str">
         <v>月下美人TYPE-E 鋭感（エイカン） GEKKABIJIN TYPE-E EIKAN</v>
@@ -1594,8 +1594,8 @@
       <c r="A35" t="str">
         <v>DLN1033</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="str">
         <v>月下美人 TYPE-F 陽/陰 GEKKABIJIN TYPE-F YOU/IN</v>
@@ -1629,8 +1629,8 @@
       <c r="A36" t="str">
         <v>DLN1034</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>2</v>
       </c>
       <c r="C36" t="str">
         <v>エメラルダスオモリグリーダー EMERALDAS OMORIG LEADER</v>
@@ -1664,8 +1664,8 @@
       <c r="A37" t="str">
         <v>DLN1035</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>HRF® ロックフィッシュフロロ HRF® ROCKFISH FLUORO</v>
@@ -1699,8 +1699,8 @@
       <c r="A38" t="str">
         <v>DLN1036</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>2</v>
       </c>
       <c r="C38" t="str">
         <v>UVF 紅牙 デュラセンサー×8＋Si2 UVF KOGA DURA SENSOR×8＋Si2</v>
@@ -1734,8 +1734,8 @@
       <c r="A39" t="str">
         <v>DLN1037</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>2</v>
       </c>
       <c r="C39" t="str">
         <v>タチメタルEX SG TACHIMETAL EX SEAGREEN</v>
@@ -1769,8 +1769,8 @@
       <c r="A40" t="str">
         <v>DLN1038</v>
       </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="B40">
+        <v>2</v>
       </c>
       <c r="C40" t="str">
         <v>ベイトキャスティングデュラセンサー×12EX+Si3 BAIT CASTING DURA SENSOR X 12EX+SI3</v>
@@ -1804,8 +1804,8 @@
       <c r="A41" t="str">
         <v>DLN1039</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>2</v>
       </c>
       <c r="C41" t="str">
         <v>月下美人 TYPE-N 煌 GEKKABIJIN TYPE-N KIRAMEKI</v>
@@ -1839,8 +1839,8 @@
       <c r="A42" t="str">
         <v>DLN1040</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>2</v>
       </c>
       <c r="C42" t="str">
         <v>テンカラ フライライン Y TENKARA FLYLINE Y</v>
@@ -1874,8 +1874,8 @@
       <c r="A43" t="str">
         <v>DLN1041</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>2</v>
       </c>
       <c r="C43" t="str">
         <v>モアザンリーダーEX II TYPE-N（ナイロン） morethan LEADER EX II TYPE-N（NYLON）</v>
@@ -1909,8 +1909,8 @@
       <c r="A44" t="str">
         <v>DLN1042</v>
       </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="B44">
+        <v>2</v>
       </c>
       <c r="C44" t="str">
         <v>月下美人 TYPE-E 白 GEKKABIJIN TYPE-E HAKU</v>
@@ -1944,8 +1944,8 @@
       <c r="A45" t="str">
         <v>DLN1043</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="B45">
+        <v>2</v>
       </c>
       <c r="C45" t="str">
         <v>渓流ガンマ KEIRYU GAMMA</v>
@@ -1979,8 +1979,8 @@
       <c r="A46" t="str">
         <v>DLN1044</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="B46">
+        <v>2</v>
       </c>
       <c r="C46" t="str">
         <v>テンカラ テーパーライン TENKARA TAPER LINE</v>
@@ -2014,8 +2014,8 @@
       <c r="A47" t="str">
         <v>DLN1045</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
+      <c r="B47">
+        <v>2</v>
       </c>
       <c r="C47" t="str">
         <v>タフロン テンカラレベルライン TOUGHRON TENKARA LEVEL</v>
@@ -2049,8 +2049,8 @@
       <c r="A48" t="str">
         <v>DLN1046</v>
       </c>
-      <c r="B48" t="str">
-        <v/>
+      <c r="B48">
+        <v>2</v>
       </c>
       <c r="C48" t="str">
         <v>UVF 月下美人デュラヘビー×4＋1＋Si2 UVF GEKKABIJIN DURAHEAVY×4＋1＋Si2</v>

--- a/GearSage-client/pkgGear/data_raw/daiwa_line_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_line_import.xlsx
@@ -458,7 +458,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H2" t="str">
-        <v>images/daiwa_lines/フィネス ブレイブ Z FINESSE BRAVE Z_FinesseBraveZ_4lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20FINESSE%20BRAVE%20Z_FinesseBraveZ_4lb.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H3" t="str">
-        <v>images/daiwa_lines/BASS-Xフロロ 240 BASS-X FLUORO 240_BASS-X-FLUORO-240_8.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/BASS-X%E3%83%95%E3%83%AD%E3%83%AD%20240%20BASS-X%20FLUORO%20240_BASS-X-FLUORO-240_8.png</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v>PE</v>
       </c>
       <c r="H4" t="str">
-        <v>images/daiwa_lines/UVF タトゥーラ センサー×8＋Si2 UVF TATULA SENSOR×8+Si2_UVFTatulaSensor8-Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20TATULA%20SENSOR%C3%978%2BSi2_UVFTatulaSensor8-Si2.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -563,7 +563,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H5" t="str">
-        <v>images/daiwa_lines/スティーズ フロロ X’LINK STEEZ FLUORO X’LINK_SteezFluoroXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%95%E3%83%AD%E3%83%AD%20X%E2%80%99LINK%20STEEZ%20FLUORO%20X%E2%80%99LINK_SteezFluoroXLink.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -598,7 +598,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H6" t="str">
-        <v>images/daiwa_lines/モンスター ブレイブ Z MONSTER BRAVE Z_MonsterBraveZ_18lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%83%B3%E3%82%B9%E3%82%BF%E3%83%BC%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20MONSTER%20BRAVE%20Z_MonsterBraveZ_18lb.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -633,7 +633,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>images/daiwa_lines/スティーズ デュラブラ マックス STEEZ DURABRA MAX_SteezDurabraMax.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20%E3%83%9E%E3%83%83%E3%82%AF%E3%82%B9%20STEEZ%20DURABRA%20MAX_SteezDurabraMax.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H8" t="str">
-        <v>images/daiwa_lines/バス-X フロロ BASS-X FLUORO_BASS-X100m_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%95%E3%83%AD%E3%83%AD%20BASS-X%20FLUORO_BASS-X100m_1.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -703,7 +703,7 @@
         <v>PE</v>
       </c>
       <c r="H9" t="str">
-        <v>images/daiwa_lines/UVF フロッグデュラセンサー×8＋Si2 UVF FROG DURA SENSOR×8+Si2_UVFFrogDuraSensor8PlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%95%E3%83%AD%E3%83%83%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20FROG%20DURA%20SENSOR%C3%978%2BSi2_UVFFrogDuraSensor8PlusSi2.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -738,7 +738,7 @@
         <v>Nylon</v>
       </c>
       <c r="H10" t="str">
-        <v>images/daiwa_lines/バス-X ナイロン BASS-X NYLON_BassXNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20BASS-X%20NYLON_BassXNylon.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -773,7 +773,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H11" t="str">
-        <v>images/daiwa_lines/スティーズフロロ タフネス STEEZ FLUORO TOUGHNESS_STEEZ-FLUORO-TOUGHNESS.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%95%E3%83%AD%E3%83%AD%20%E3%82%BF%E3%83%95%E3%83%8D%E3%82%B9%20STEEZ%20FLUORO%20TOUGHNESS_STEEZ-FLUORO-TOUGHNESS.png</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -808,7 +808,7 @@
         <v>Nylon</v>
       </c>
       <c r="H12" t="str">
-        <v>images/daiwa_lines/タトゥーラ タイプ ナイロン TATULA Type NYLON_TatulaTypeNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BF%E3%82%A4%E3%83%97%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20TATULA%20Type%20NYLON_TatulaTypeNylon.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -843,7 +843,7 @@
         <v>Ester</v>
       </c>
       <c r="H13" t="str">
-        <v>images/daiwa_lines/プレッソエリアエステル TT PRESSO AREA ESTER TECHNICAL TUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%82%A8%E3%82%B9%E3%83%86%E3%83%AB%20TT%20PRESSO%20AREA%20ESTER%20TECHNICAL%20TUNE_main.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -878,7 +878,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H14" t="str">
-        <v>images/daiwa_lines/トラウトフロロリーダー TROUT FLUORO LEADER_TroutFluoroLeader_3lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20TROUT%20FLUORO%20LEADER_TroutFluoroLeader_3lb.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v>Nylon</v>
       </c>
       <c r="H15" t="str">
-        <v>images/daiwa_lines/プレッソエリアデュラブラMAX PRESSO AREA DURABRAMAX_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9MAX%20PRESSO%20AREA%20DURABRAMAX_main.png</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -948,7 +948,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H16" t="str">
-        <v>images/daiwa_lines/プレッソ　エリア　TYPE-F PRESSO AREA TYPE F_PressoAreaTypeF_100.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%80%80%E3%82%A8%E3%83%AA%E3%82%A2%E3%80%80TYPE-F%20PRESSO%20AREA%20TYPE%20F_PressoAreaTypeF_100.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>images/daiwa_lines/プレッソ タイプN PRESSO TYPE N_PressoTypeN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%BF%E3%82%A4%E3%83%97N%20PRESSO%20TYPE%20N_PressoTypeN.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1018,7 +1018,7 @@
         <v>PE</v>
       </c>
       <c r="H18" t="str">
-        <v>images/daiwa_lines/UVFプレッソエリアデュラセンサー×8EX+Si3 UVF PRESSO AREA DURA SENSOR X8EX+SI3_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978EX%2BSi3%20UVF%20PRESSO%20AREA%20DURA%20SENSOR%20X8EX%2BSI3_main.png</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H19" t="str">
-        <v>images/daiwa_lines/月下美人フロロリーダー GEKKABIJIN FLUORO LEADER_GekkabijinFluoroLeader_Package1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20GEKKABIJIN%20FLUORO%20LEADER_GekkabijinFluoroLeader_Package1.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1088,7 +1088,7 @@
         <v>Ester</v>
       </c>
       <c r="H20" t="str">
-        <v>images/daiwa_lines/プレッソ エリア TYPE-E PRESSO AREA TYPE-E_PressoAreaTypeE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A8%E3%83%AA%E3%82%A2%20TYPE-E%20PRESSO%20AREA%20TYPE-E_PressoAreaTypeE.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>images/daiwa_lines/UVF エメラルダスデュラセンサーX8EX+Si3 IM UVF EMERALDAS DURASENSOR X8EX+SI3 IM_4550133628382.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BCX8EX%2BSi3%20IM%20UVF%20EMERALDAS%20DURASENSOR%20X8EX%2BSI3%20IM_4550133628382.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1158,7 +1158,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H22" t="str">
-        <v>images/daiwa_lines/紅牙フロロリーダーEX KOHGA FLUORO LEADER EX_KOHGA_FLUOROLEADER_EX_package_ol.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E7%B4%85%E7%89%99%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20KOHGA%20FLUORO%20LEADER%20EX_KOHGA_FLUOROLEADER_EX_package_ol.png</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1193,7 +1193,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H23" t="str">
-        <v>images/daiwa_lines/フロロショックリーダーX FLUORO SHOCK LEADER X_FluoroShockLeaderX_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%83%AD%E3%83%AD%E3%82%B7%E3%83%A7%E3%83%83%E3%82%AF%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCX%20FLUORO%20SHOCK%20LEADER%20X_FluoroShockLeaderX_Package.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H24" t="str">
-        <v>images/daiwa_lines/モアザンリーダーEX II TYPE-F（フロロ） morethan LEADER EX II TYPE-F（FLUORO）_MT_LeaderType-F2_NaturalClear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-F%EF%BC%88%E3%83%95%E3%83%AD%E3%83%AD%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-F%EF%BC%88FLUORO%EF%BC%89_MT_LeaderType-F2_NaturalClear.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1263,7 +1263,7 @@
         <v>Nylon</v>
       </c>
       <c r="H25" t="str">
-        <v>images/daiwa_lines/シルバークリーク TYPE-N（ナイロン） SILVER CREEK TYPE-N_SilverCreekType-N.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20SILVER%20CREEK%20TYPE-N_SilverCreekType-N.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>images/daiwa_lines/UVF ソルティガデュラセンサー8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2_UVFSGDuraSensor8plusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC8%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFSGDuraSensor8plusSi2.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1333,7 +1333,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H27" t="str">
-        <v>images/daiwa_lines/ソルティガ フロロリーダー X’LINK（クロスリンク） SALTIGA FLUORO LEADER X’LINK_SG_FuluroLaederXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20X%E2%80%99LINK%EF%BC%88%E3%82%AF%E3%83%AD%E3%82%B9%E3%83%AA%E3%83%B3%E3%82%AF%EF%BC%89%20SALTIGA%20FLUORO%20LEADER%20X%E2%80%99LINK_SG_FuluroLaederXLink.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1368,7 +1368,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>images/daiwa_lines/UVF ソルティガ SJ デュラセンサー×8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2_SGSJDURA8P.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20SJ%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_SGSJDURA8P.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v>Nylon</v>
       </c>
       <c r="H29" t="str">
-        <v>images/daiwa_lines/モアザンデュラブラ MAX MORETHAN DURABRA MAX_MORETHAN-DURABRA-MAX.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20MAX%20MORETHAN%20DURABRA%20MAX_MORETHAN-DURABRA-MAX.png</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v>PE</v>
       </c>
       <c r="H30" t="str">
-        <v>images/daiwa_lines/UVF モアザン デュラセンサー×8＋Si² UVF MORETHAN DURASENSOR X8BRAID +Si²_UVF_MT_DuraSensor8BraidPlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi%C2%B2%20UVF%20MORETHAN%20DURASENSOR%20X8BRAID%20%2BSi%C2%B2_UVF_MT_DuraSensor8BraidPlusSi2.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1473,7 +1473,7 @@
         <v>PE</v>
       </c>
       <c r="H31" t="str">
-        <v>images/daiwa_lines/UVF ソルティガデュラセンサー×12EX+Si3 UVF SALTIGA DURA SENSOR×12EX+Si3_SALTIGA-DURASENSOR-12EX.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20UVF%20SALTIGA%20DURA%20SENSOR%C3%9712EX%2BSi3_SALTIGA-DURASENSOR-12EX.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v>PE</v>
       </c>
       <c r="H32" t="str">
-        <v>images/daiwa_lines/UVF月下美人デュラセンサー＋Si² UVF GEKKABIJIN DURA SENSOR＋Si²_UVFGekkabijinDuraSensorSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%EF%BC%8BSi%C2%B2%20UVF%20GEKKABIJIN%20DURA%20SENSOR%EF%BC%8BSi%C2%B2_UVFGekkabijinDuraSensorSi2.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1543,7 +1543,7 @@
         <v>Nylon</v>
       </c>
       <c r="H33" t="str">
-        <v>images/daiwa_lines/ソルティガ ナイロンリーダー SALTIGA NYLON LEADER_SG_NylonLaeder40LB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20SALTIGA%20NYLON%20LEADER_SG_NylonLaeder40LB.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1578,7 +1578,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>images/daiwa_lines/月下美人TYPE-E 鋭感（エイカン） GEKKABIJIN TYPE-E EIKAN_GekkaTypeE_Eikan.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BATYPE-E%20%E9%8B%AD%E6%84%9F%EF%BC%88%E3%82%A8%E3%82%A4%E3%82%AB%E3%83%B3%EF%BC%89%20GEKKABIJIN%20TYPE-E%20EIKAN_GekkaTypeE_Eikan.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-F 陽陰 GEKKABIJIN TYPE-F YOUIN_Gekka_TypeF_Yo.jpg</v>
+        <v/>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>images/daiwa_lines/エメラルダスオモリグリーダー EMERALDAS OMORIG LEADER_omorig-leader_4550133408427_data.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%82%AA%E3%83%A2%E3%83%AA%E3%82%B0%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20EMERALDAS%20OMORIG%20LEADER_omorig-leader_4550133408427_data.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1683,7 +1683,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H37" t="str">
-        <v>images/daiwa_lines/HRF® ロックフィッシュフロロ HRF® ROCKFISH FLUORO_HRFRockFishFluoro.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/HRF%C2%AE%20%E3%83%AD%E3%83%83%E3%82%AF%E3%83%95%E3%82%A3%E3%83%83%E3%82%B7%E3%83%A5%E3%83%95%E3%83%AD%E3%83%AD%20HRF%C2%AE%20ROCKFISH%20FLUORO_HRFRockFishFluoro.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1718,7 +1718,7 @@
         <v>PE</v>
       </c>
       <c r="H38" t="str">
-        <v>images/daiwa_lines/UVF 紅牙 デュラセンサー×8＋Si2 UVF KOGA DURA SENSOR×8＋Si2_UVFKohgaDurasensor8Braid_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E7%B4%85%E7%89%99%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20KOGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFKohgaDurasensor8Braid_1.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>images/daiwa_lines/タチメタルEX SG TACHIMETAL EX SEAGREEN_TACHIMETAL-EX-SEAGREEN.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%81%E3%83%A1%E3%82%BF%E3%83%ABEX%20SG%20TACHIMETAL%20EX%20SEAGREEN_TACHIMETAL-EX-SEAGREEN.png</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1788,7 +1788,7 @@
         <v>PE</v>
       </c>
       <c r="H40" t="str">
-        <v>images/daiwa_lines/ベイトキャスティングデュラセンサー×12EX+Si3 BAIT CASTING DURA SENSOR X 12EX+SI3_BAIT_CASTING_DURA_SENSOR.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20BAIT%20CASTING%20DURA%20SENSOR%20X%2012EX%2BSI3_BAIT_CASTING_DURA_SENSOR.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1823,7 +1823,7 @@
         <v>Nylon</v>
       </c>
       <c r="H41" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-N 煌 GEKKABIJIN TYPE-N KIRAMEKI_Gekka_TypeN_Kou.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-N%20%E7%85%8C%20GEKKABIJIN%20TYPE-N%20KIRAMEKI_Gekka_TypeN_Kou.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>images/daiwa_lines/テンカラ フライライン Y TENKARA FLYLINE Y_TenkaraFryLineY.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%95%E3%83%A9%E3%82%A4%E3%83%A9%E3%82%A4%E3%83%B3%20Y%20TENKARA%20FLYLINE%20Y_TenkaraFryLineY.jpg</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1893,7 +1893,7 @@
         <v>Nylon</v>
       </c>
       <c r="H43" t="str">
-        <v>images/daiwa_lines/モアザンリーダーEX II TYPE-N（ナイロン） morethan LEADER EX II TYPE-N（NYLON）_MT_LeaderType-N2_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-N%EF%BC%88NYLON%EF%BC%89_MT_LeaderType-N2_Clear.jpg</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1928,7 +1928,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-E 白 GEKKABIJIN TYPE-E HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-E%20%E7%99%BD%20GEKKABIJIN%20TYPE-E%20HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1963,7 +1963,7 @@
         <v>Nylon</v>
       </c>
       <c r="H45" t="str">
-        <v>images/daiwa_lines/渓流ガンマ KEIRYU GAMMA_KeiryuGamma.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%B8%93%E6%B5%81%E3%82%AC%E3%83%B3%E3%83%9E%20KEIRYU%20GAMMA_KeiryuGamma.jpg</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1998,7 +1998,7 @@
         <v>Nylon</v>
       </c>
       <c r="H46" t="str">
-        <v>images/daiwa_lines/テンカラ テーパーライン TENKARA TAPER LINE_TenkaraTaperLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%86%E3%83%BC%E3%83%91%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%B3%20TENKARA%20TAPER%20LINE_TenkaraTaperLine.jpg</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2033,7 +2033,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>images/daiwa_lines/タフロン テンカラレベルライン TOUGHRON TENKARA LEVEL_ToughronTenkaraLevelLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%95%E3%83%AD%E3%83%B3%20%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%E3%83%AC%E3%83%99%E3%83%AB%E3%83%A9%E3%82%A4%E3%83%B3%20TOUGHRON%20TENKARA%20LEVEL_ToughronTenkaraLevelLine.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2068,7 +2068,7 @@
         <v>PE</v>
       </c>
       <c r="H48" t="str">
-        <v>images/daiwa_lines/UVF 月下美人デュラヘビー×4＋1＋Si2 UVF GEKKABIJIN DURAHEAVY×4＋1＋Si2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%83%98%E3%83%93%E3%83%BC%C3%974%EF%BC%8B1%EF%BC%8BSi2%20UVF%20GEKKABIJIN%20DURAHEAVY%C3%974%EF%BC%8B1%EF%BC%8BSi2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
